--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.623516054654427</v>
+        <v>1.401321358881344</v>
       </c>
       <c r="D2" t="n">
-        <v>8.450300582417492</v>
+        <v>1.373173844642843</v>
       </c>
       <c r="E2" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F2" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.12387224346505</v>
+        <v>3.107629239563071</v>
       </c>
       <c r="D3" t="n">
-        <v>10.72732414766348</v>
+        <v>1.743190173995316</v>
       </c>
       <c r="E3" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F3" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.32717601839476</v>
+        <v>4.278166102989148</v>
       </c>
       <c r="D4" t="n">
-        <v>3.711115269458757</v>
+        <v>0.603056231287048</v>
       </c>
       <c r="E4" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F4" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.969049532609153</v>
+        <v>1.457470549048987</v>
       </c>
       <c r="D5" t="n">
-        <v>8.838795903960445</v>
+        <v>1.436304334393572</v>
       </c>
       <c r="E5" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F5" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.65622897344485</v>
+        <v>2.544137208184787</v>
       </c>
       <c r="D6" t="n">
-        <v>14.0574219226397</v>
+        <v>2.284331062428952</v>
       </c>
       <c r="E6" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F6" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.55968061280127</v>
+        <v>3.665948099580207</v>
       </c>
       <c r="D7" t="n">
-        <v>22.60190413212754</v>
+        <v>3.672809421470726</v>
       </c>
       <c r="E7" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F7" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.88675263090591</v>
+        <v>4.531597302522211</v>
       </c>
       <c r="D8" t="n">
-        <v>27.73239373233017</v>
+        <v>4.506513981503653</v>
       </c>
       <c r="E8" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F8" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.62959551699928</v>
+        <v>5.789809271512383</v>
       </c>
       <c r="D9" t="n">
-        <v>35.48844545165793</v>
+        <v>5.766872385894414</v>
       </c>
       <c r="E9" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F9" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>75.19236058830269</v>
+        <v>12.21875859559919</v>
       </c>
       <c r="D10" t="n">
-        <v>75.00685491835354</v>
+        <v>12.18861392423245</v>
       </c>
       <c r="E10" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F10" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.03101673529856</v>
+        <v>6.342540219486017</v>
       </c>
       <c r="D11" t="n">
-        <v>38.84538216934977</v>
+        <v>6.312374602519338</v>
       </c>
       <c r="E11" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F11" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>57.9130189760122</v>
+        <v>9.410865583601984</v>
       </c>
       <c r="D12" t="n">
-        <v>57.72878802868753</v>
+        <v>9.380928054661725</v>
       </c>
       <c r="E12" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F12" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>17.48297116416617</v>
+        <v>2.840982814177002</v>
       </c>
       <c r="D13" t="n">
-        <v>17.66512985500941</v>
+        <v>2.87058360143903</v>
       </c>
       <c r="E13" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F13" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.2258545627071</v>
+        <v>5.074201366439905</v>
       </c>
       <c r="D14" t="n">
-        <v>31.4114563813813</v>
+        <v>5.104361661974461</v>
       </c>
       <c r="E14" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F14" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20382875054235</v>
+        <v>2.795622171963132</v>
       </c>
       <c r="D15" t="n">
-        <v>17.19214243875701</v>
+        <v>2.793723146298014</v>
       </c>
       <c r="E15" t="n">
-        <v>17.99244058594533</v>
+        <v>2.923771595216116</v>
       </c>
       <c r="F15" t="n">
-        <v>19.50704711404404</v>
+        <v>3.169895156032156</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
